--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_biobio.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_biobio.xlsx
@@ -404,7 +404,7 @@
         <v>21.58212593844364</v>
       </c>
       <c r="D2">
-        <v>1.76115143013966</v>
+        <v>2.840997186313283</v>
       </c>
       <c r="E2">
         <v>22.45099901490019</v>
@@ -429,7 +429,7 @@
         <v>29.48246386572036</v>
       </c>
       <c r="D3">
-        <v>1.619005682413873</v>
+        <v>3.097524772335219</v>
       </c>
       <c r="E3">
         <v>19.95708669927864</v>
@@ -454,7 +454,7 @@
         <v>23.87621054122479</v>
       </c>
       <c r="D4">
-        <v>1.642855065297694</v>
+        <v>2.703182579564489</v>
       </c>
       <c r="E4">
         <v>22.9959059693608</v>
@@ -479,7 +479,7 @@
         <v>25.94185894928953</v>
       </c>
       <c r="D5">
-        <v>1.350528169014085</v>
+        <v>2.078861788617886</v>
       </c>
       <c r="E5">
         <v>27.63837914762939</v>
@@ -504,7 +504,7 @@
         <v>27.92823482654857</v>
       </c>
       <c r="D6">
-        <v>1.624066390041494</v>
+        <v>2.972156598042524</v>
       </c>
       <c r="E6">
         <v>20.82366996978003</v>
@@ -529,7 +529,7 @@
         <v>25.98470023127557</v>
       </c>
       <c r="D7">
-        <v>1.482800464281946</v>
+        <v>2.412239292764569</v>
       </c>
       <c r="E7">
         <v>24.75828215644191</v>
@@ -554,7 +554,7 @@
         <v>26.36281530223856</v>
       </c>
       <c r="D8">
-        <v>1.547932893948472</v>
+        <v>2.615099114297765</v>
       </c>
       <c r="E8">
         <v>23.23143249069175</v>
@@ -579,7 +579,7 @@
         <v>29.05917126763705</v>
       </c>
       <c r="D9">
-        <v>1.801893239006351</v>
+        <v>3.782432603467916</v>
       </c>
       <c r="E9">
         <v>17.00224515999455</v>
@@ -604,7 +604,7 @@
         <v>25.99586621570838</v>
       </c>
       <c r="D10">
-        <v>1.520571428571428</v>
+        <v>2.514528703047484</v>
       </c>
       <c r="E10">
         <v>23.99115846746769</v>
@@ -629,7 +629,7 @@
         <v>25.62536358347877</v>
       </c>
       <c r="D11">
-        <v>1.474416916834362</v>
+        <v>2.369777306468717</v>
       </c>
       <c r="E11">
         <v>25.14431986347941</v>
@@ -654,7 +654,7 @@
         <v>25.21558872305141</v>
       </c>
       <c r="D12">
-        <v>1.487114143614616</v>
+        <v>2.379323951071945</v>
       </c>
       <c r="E12">
         <v>25.13014592870482</v>
@@ -679,7 +679,7 @@
         <v>22.50360608444794</v>
       </c>
       <c r="D13">
-        <v>1.680753760537771</v>
+        <v>2.703176924099429</v>
       </c>
       <c r="E13">
         <v>23.19384210634493</v>
@@ -704,7 +704,7 @@
         <v>28.80243451279909</v>
       </c>
       <c r="D14">
-        <v>1.611907280946427</v>
+        <v>3.008797127468582</v>
       </c>
       <c r="E14">
         <v>20.51112093091766</v>
@@ -729,7 +729,7 @@
         <v>27.18054377247202</v>
       </c>
       <c r="D15">
-        <v>1.666195476575121</v>
+        <v>3.045398622047244</v>
       </c>
       <c r="E15">
         <v>20.52058875508092</v>
@@ -754,7 +754,7 @@
         <v>29.92016660881638</v>
       </c>
       <c r="D16">
-        <v>1.565548159217498</v>
+        <v>2.945054945054945</v>
       </c>
       <c r="E16">
         <v>20.72014826581943</v>
@@ -779,7 +779,7 @@
         <v>24.6606334841629</v>
       </c>
       <c r="D17">
-        <v>1.60844250363901</v>
+        <v>2.665862484921592</v>
       </c>
       <c r="E17">
         <v>23.13058035714285</v>
@@ -804,7 +804,7 @@
         <v>26.65580890336591</v>
       </c>
       <c r="D18">
-        <v>1.612371434823838</v>
+        <v>2.827683254445439</v>
       </c>
       <c r="E18">
         <v>21.82726942730293</v>
@@ -829,7 +829,7 @@
         <v>29.9431853655491</v>
       </c>
       <c r="D19">
-        <v>1.669480925578487</v>
+        <v>3.338265944143393</v>
       </c>
       <c r="E19">
         <v>18.73413767521768</v>
@@ -854,7 +854,7 @@
         <v>31.61465400271371</v>
       </c>
       <c r="D20">
-        <v>1.700507614213198</v>
+        <v>3.677644710578842</v>
       </c>
       <c r="E20">
         <v>17.12235133287765</v>
@@ -879,7 +879,7 @@
         <v>28.11850385349643</v>
       </c>
       <c r="D21">
-        <v>1.678614665179101</v>
+        <v>3.179202445713258</v>
       </c>
       <c r="E21">
         <v>19.71163219368675</v>
@@ -904,7 +904,7 @@
         <v>25.1705565529623</v>
       </c>
       <c r="D22">
-        <v>1.368550368550369</v>
+        <v>2.087706146926537</v>
       </c>
       <c r="E22">
         <v>27.67634854771784</v>
@@ -929,7 +929,7 @@
         <v>25.90260886154433</v>
       </c>
       <c r="D23">
-        <v>1.646666143092751</v>
+        <v>2.871405094494659</v>
       </c>
       <c r="E23">
         <v>21.66765578635015</v>
@@ -954,7 +954,7 @@
         <v>26.70709367696292</v>
       </c>
       <c r="D24">
-        <v>1.528974309445625</v>
+        <v>2.584231145935358</v>
       </c>
       <c r="E24">
         <v>23.39507351537139</v>
@@ -979,7 +979,7 @@
         <v>26.00816489096883</v>
       </c>
       <c r="D25">
-        <v>1.582322357019064</v>
+        <v>2.688888888888889</v>
       </c>
       <c r="E25">
         <v>22.7882855399634</v>
@@ -1004,7 +1004,7 @@
         <v>27.84565916398714</v>
       </c>
       <c r="D26">
-        <v>1.542937037705214</v>
+        <v>2.705203226316622</v>
       </c>
       <c r="E26">
         <v>22.42914405306658</v>
@@ -1029,7 +1029,7 @@
         <v>24.31785543322164</v>
       </c>
       <c r="D27">
-        <v>1.658265528874777</v>
+        <v>2.778849351513136</v>
       </c>
       <c r="E27">
         <v>22.44867487868608</v>
@@ -1054,7 +1054,7 @@
         <v>27.35012415750266</v>
       </c>
       <c r="D28">
-        <v>1.300876788186433</v>
+        <v>2.019340974212034</v>
       </c>
       <c r="E28">
         <v>27.99839550742078</v>
@@ -1079,7 +1079,7 @@
         <v>25.9498787388844</v>
       </c>
       <c r="D29">
-        <v>1.414037494284408</v>
+        <v>2.233658360418924</v>
       </c>
       <c r="E29">
         <v>26.22407424945544</v>
@@ -1104,7 +1104,7 @@
         <v>23.56959863364645</v>
       </c>
       <c r="D30">
-        <v>1.433292533659731</v>
+        <v>2.164510166358595</v>
       </c>
       <c r="E30">
         <v>27.21327967806841</v>
@@ -1129,7 +1129,7 @@
         <v>26.17313915857605</v>
       </c>
       <c r="D31">
-        <v>1.571519389701208</v>
+        <v>2.669546436285097</v>
       </c>
       <c r="E31">
         <v>22.89245982694685</v>
@@ -1154,7 +1154,7 @@
         <v>25.80314740664866</v>
       </c>
       <c r="D32">
-        <v>1.511045448149712</v>
+        <v>2.476706642066421</v>
       </c>
       <c r="E32">
         <v>24.29676117897568</v>
@@ -1179,7 +1179,7 @@
         <v>25.85929296464823</v>
       </c>
       <c r="D33">
-        <v>1.369081847805252</v>
+        <v>2.119436201780415</v>
       </c>
       <c r="E33">
         <v>27.26647518103483</v>
@@ -1204,7 +1204,7 @@
         <v>34.24711180732329</v>
       </c>
       <c r="D34">
-        <v>1.777584406543683</v>
+        <v>4.543594306049823</v>
       </c>
       <c r="E34">
         <v>14.08521303258146</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_biobio.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_biobio.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>21.58212593844364</v>
+      </c>
+      <c r="C2">
         <v>35.19890849655096</v>
-      </c>
-      <c r="C2">
-        <v>21.58212593844364</v>
       </c>
       <c r="D2">
         <v>2.840997186313283</v>
       </c>
       <c r="E2">
+        <v>13.76577595384608</v>
+      </c>
+      <c r="F2">
+        <v>63.78322503125372</v>
+      </c>
+      <c r="G2">
         <v>22.45099901490019</v>
-      </c>
-      <c r="F2">
-        <v>63.78322503125374</v>
-      </c>
-      <c r="G2">
-        <v>13.76577595384609</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>29.48246386572036</v>
+      </c>
+      <c r="C3">
         <v>32.28384188986168</v>
-      </c>
-      <c r="C3">
-        <v>29.48246386572036</v>
       </c>
       <c r="D3">
         <v>3.097524772335219</v>
       </c>
       <c r="E3">
-        <v>19.95708669927864</v>
+        <v>18.22534286606406</v>
       </c>
       <c r="F3">
         <v>61.81757043465729</v>
       </c>
       <c r="G3">
-        <v>18.22534286606406</v>
+        <v>19.95708669927864</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>23.87621054122479</v>
+      </c>
+      <c r="C4">
         <v>36.99343165200148</v>
-      </c>
-      <c r="C4">
-        <v>23.87621054122479</v>
       </c>
       <c r="D4">
         <v>2.703182579564489</v>
       </c>
       <c r="E4">
-        <v>22.9959059693608</v>
+        <v>14.84196161296003</v>
       </c>
       <c r="F4">
         <v>62.16213241767917</v>
       </c>
       <c r="G4">
-        <v>14.84196161296003</v>
+        <v>22.9959059693608</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>25.94185894928953</v>
+      </c>
+      <c r="C5">
         <v>48.10324599139616</v>
-      </c>
-      <c r="C5">
-        <v>25.94185894928953</v>
       </c>
       <c r="D5">
         <v>2.078861788617886</v>
       </c>
       <c r="E5">
-        <v>27.63837914762939</v>
+        <v>14.90525054303049</v>
       </c>
       <c r="F5">
         <v>57.45637030934013</v>
       </c>
       <c r="G5">
-        <v>14.90525054303049</v>
+        <v>27.63837914762939</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>27.92823482654857</v>
+      </c>
+      <c r="C6">
         <v>33.64560267983875</v>
-      </c>
-      <c r="C6">
-        <v>27.92823482654857</v>
       </c>
       <c r="D6">
         <v>2.972156598042524</v>
       </c>
       <c r="E6">
-        <v>20.82366996978003</v>
+        <v>17.28512193407829</v>
       </c>
       <c r="F6">
         <v>61.89120809614168</v>
       </c>
       <c r="G6">
-        <v>17.28512193407829</v>
+        <v>20.82366996978003</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>25.98470023127557</v>
+      </c>
+      <c r="C7">
         <v>41.45525707169543</v>
-      </c>
-      <c r="C7">
-        <v>25.98470023127557</v>
       </c>
       <c r="D7">
         <v>2.412239292764569</v>
       </c>
       <c r="E7">
-        <v>24.75828215644191</v>
+        <v>15.51881680443698</v>
       </c>
       <c r="F7">
         <v>59.7229010391211</v>
       </c>
       <c r="G7">
-        <v>15.51881680443698</v>
+        <v>24.75828215644191</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>26.36281530223856</v>
+      </c>
+      <c r="C8">
         <v>38.23946842139217</v>
-      </c>
-      <c r="C8">
-        <v>26.36281530223856</v>
       </c>
       <c r="D8">
         <v>2.615099114297765</v>
       </c>
       <c r="E8">
-        <v>23.23143249069175</v>
+        <v>16.01606897903194</v>
       </c>
       <c r="F8">
         <v>60.75249853027631</v>
       </c>
       <c r="G8">
-        <v>16.01606897903194</v>
+        <v>23.23143249069175</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>29.05917126763705</v>
+      </c>
+      <c r="C9">
         <v>26.43801238079304</v>
-      </c>
-      <c r="C9">
-        <v>29.05917126763705</v>
       </c>
       <c r="D9">
         <v>3.782432603467916</v>
       </c>
       <c r="E9">
-        <v>17.00224515999455</v>
+        <v>18.68790841468751</v>
       </c>
       <c r="F9">
         <v>64.30984642531794</v>
       </c>
       <c r="G9">
-        <v>18.68790841468751</v>
+        <v>17.00224515999454</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>25.99586621570838</v>
+      </c>
+      <c r="C10">
         <v>39.76888387824126</v>
-      </c>
-      <c r="C10">
-        <v>25.99586621570838</v>
       </c>
       <c r="D10">
         <v>2.514528703047484</v>
       </c>
       <c r="E10">
-        <v>23.99115846746769</v>
+        <v>15.6823849467241</v>
       </c>
       <c r="F10">
-        <v>60.3264565858082</v>
+        <v>60.32645658580821</v>
       </c>
       <c r="G10">
-        <v>15.6823849467241</v>
+        <v>23.9911584674677</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>25.62536358347877</v>
+      </c>
+      <c r="C11">
         <v>42.19805790486419</v>
-      </c>
-      <c r="C11">
-        <v>25.62536358347877</v>
       </c>
       <c r="D11">
         <v>2.369777306468717</v>
       </c>
       <c r="E11">
-        <v>25.14431986347941</v>
+        <v>15.26924153745651</v>
       </c>
       <c r="F11">
         <v>59.58643859906409</v>
       </c>
       <c r="G11">
-        <v>15.26924153745651</v>
+        <v>25.14431986347941</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>25.21558872305141</v>
+      </c>
+      <c r="C12">
         <v>42.02874516307352</v>
-      </c>
-      <c r="C12">
-        <v>25.21558872305141</v>
       </c>
       <c r="D12">
         <v>2.379323951071945</v>
       </c>
       <c r="E12">
-        <v>25.13014592870482</v>
+        <v>15.07709596919466</v>
       </c>
       <c r="F12">
         <v>59.79275810210051</v>
       </c>
       <c r="G12">
-        <v>15.07709596919466</v>
+        <v>25.13014592870482</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>22.50360608444794</v>
+      </c>
+      <c r="C13">
         <v>36.9935090479937</v>
-      </c>
-      <c r="C13">
-        <v>22.50360608444794</v>
       </c>
       <c r="D13">
         <v>2.703176924099429</v>
       </c>
       <c r="E13">
-        <v>23.19384210634493</v>
+        <v>14.10909913057777</v>
       </c>
       <c r="F13">
         <v>62.6970587630773</v>
       </c>
       <c r="G13">
-        <v>14.10909913057777</v>
+        <v>23.19384210634493</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>28.80243451279909</v>
+      </c>
+      <c r="C14">
         <v>33.23587326212781</v>
-      </c>
-      <c r="C14">
-        <v>28.80243451279909</v>
       </c>
       <c r="D14">
         <v>3.008797127468582</v>
       </c>
       <c r="E14">
-        <v>20.51112093091766</v>
+        <v>17.77507733097658</v>
       </c>
       <c r="F14">
         <v>61.71380173810575</v>
       </c>
       <c r="G14">
-        <v>17.77507733097658</v>
+        <v>20.51112093091766</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>27.18054377247202</v>
+      </c>
+      <c r="C15">
         <v>32.83642386781401</v>
-      </c>
-      <c r="C15">
-        <v>27.18054377247202</v>
       </c>
       <c r="D15">
         <v>3.045398622047244</v>
       </c>
       <c r="E15">
-        <v>20.52058875508092</v>
+        <v>16.98603852659749</v>
       </c>
       <c r="F15">
         <v>62.4933727183216</v>
       </c>
       <c r="G15">
-        <v>16.98603852659749</v>
+        <v>20.52058875508092</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>29.92016660881638</v>
+      </c>
+      <c r="C16">
         <v>33.95522388059701</v>
-      </c>
-      <c r="C16">
-        <v>29.92016660881638</v>
       </c>
       <c r="D16">
         <v>2.945054945054945</v>
       </c>
       <c r="E16">
-        <v>20.72014826581943</v>
+        <v>18.2578766216574</v>
       </c>
       <c r="F16">
         <v>61.02197511252317</v>
       </c>
       <c r="G16">
-        <v>18.2578766216574</v>
+        <v>20.72014826581943</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>24.6606334841629</v>
+      </c>
+      <c r="C17">
         <v>37.51131221719457</v>
-      </c>
-      <c r="C17">
-        <v>24.6606334841629</v>
       </c>
       <c r="D17">
         <v>2.665862484921592</v>
       </c>
       <c r="E17">
-        <v>23.13058035714285</v>
+        <v>15.20647321428572</v>
       </c>
       <c r="F17">
-        <v>61.66294642857142</v>
+        <v>61.66294642857143</v>
       </c>
       <c r="G17">
-        <v>15.20647321428571</v>
+        <v>23.13058035714286</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>26.65580890336591</v>
+      </c>
+      <c r="C18">
         <v>35.36463988418386</v>
-      </c>
-      <c r="C18">
-        <v>26.65580890336591</v>
       </c>
       <c r="D18">
         <v>2.827683254445439</v>
       </c>
       <c r="E18">
-        <v>21.82726942730293</v>
+        <v>16.45212632284366</v>
       </c>
       <c r="F18">
-        <v>61.7206042498534</v>
+        <v>61.72060424985341</v>
       </c>
       <c r="G18">
-        <v>16.45212632284366</v>
+        <v>21.82726942730294</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>29.9431853655491</v>
+      </c>
+      <c r="C19">
         <v>29.95567209839545</v>
-      </c>
-      <c r="C19">
-        <v>29.9431853655491</v>
       </c>
       <c r="D19">
         <v>3.338265944143393</v>
       </c>
       <c r="E19">
+        <v>18.72632853070946</v>
+      </c>
+      <c r="F19">
+        <v>62.53953379407285</v>
+      </c>
+      <c r="G19">
         <v>18.73413767521768</v>
-      </c>
-      <c r="F19">
-        <v>62.53953379407286</v>
-      </c>
-      <c r="G19">
-        <v>18.72632853070946</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>31.61465400271371</v>
+      </c>
+      <c r="C20">
         <v>27.19131614654003</v>
-      </c>
-      <c r="C20">
-        <v>31.61465400271371</v>
       </c>
       <c r="D20">
         <v>3.677644710578842</v>
       </c>
       <c r="E20">
-        <v>17.12235133287765</v>
+        <v>19.90772385509228</v>
       </c>
       <c r="F20">
         <v>62.96992481203007</v>
       </c>
       <c r="G20">
-        <v>19.90772385509228</v>
+        <v>17.12235133287765</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>28.11850385349643</v>
+      </c>
+      <c r="C21">
         <v>31.45442975323481</v>
-      </c>
-      <c r="C21">
-        <v>28.11850385349643</v>
       </c>
       <c r="D21">
         <v>3.179202445713258</v>
       </c>
       <c r="E21">
-        <v>19.71163219368675</v>
+        <v>17.62109852714415</v>
       </c>
       <c r="F21">
         <v>62.6672692791691</v>
       </c>
       <c r="G21">
-        <v>17.62109852714415</v>
+        <v>19.71163219368675</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>25.1705565529623</v>
+      </c>
+      <c r="C22">
         <v>47.89946140035907</v>
-      </c>
-      <c r="C22">
-        <v>25.1705565529623</v>
       </c>
       <c r="D22">
         <v>2.087706146926537</v>
       </c>
       <c r="E22">
-        <v>27.67634854771784</v>
+        <v>14.54356846473029</v>
       </c>
       <c r="F22">
         <v>57.78008298755187</v>
       </c>
       <c r="G22">
-        <v>14.54356846473029</v>
+        <v>27.67634854771784</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>25.90260886154433</v>
+      </c>
+      <c r="C23">
         <v>34.82615538703677</v>
-      </c>
-      <c r="C23">
-        <v>25.90260886154433</v>
       </c>
       <c r="D23">
         <v>2.871405094494659</v>
       </c>
       <c r="E23">
-        <v>21.66765578635015</v>
+        <v>16.11572700296736</v>
       </c>
       <c r="F23">
         <v>62.21661721068249</v>
       </c>
       <c r="G23">
-        <v>16.11572700296736</v>
+        <v>21.66765578635015</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>26.70709367696292</v>
+      </c>
+      <c r="C24">
         <v>38.6962289179458</v>
-      </c>
-      <c r="C24">
-        <v>26.70709367696292</v>
       </c>
       <c r="D24">
         <v>2.584231145935358</v>
       </c>
       <c r="E24">
-        <v>23.39507351537139</v>
+        <v>16.14664884475845</v>
       </c>
       <c r="F24">
         <v>60.45827763987015</v>
       </c>
       <c r="G24">
-        <v>16.14664884475845</v>
+        <v>23.39507351537139</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>26.00816489096883</v>
+      </c>
+      <c r="C25">
         <v>37.1900826446281</v>
-      </c>
-      <c r="C25">
-        <v>26.00816489096883</v>
       </c>
       <c r="D25">
         <v>2.688888888888889</v>
       </c>
       <c r="E25">
-        <v>22.7882855399634</v>
+        <v>15.93654667480171</v>
       </c>
       <c r="F25">
         <v>61.27516778523491</v>
       </c>
       <c r="G25">
-        <v>15.93654667480171</v>
+        <v>22.7882855399634</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>27.84565916398714</v>
+      </c>
+      <c r="C26">
         <v>36.96579947383805</v>
-      </c>
-      <c r="C26">
-        <v>27.84565916398714</v>
       </c>
       <c r="D26">
         <v>2.705203226316622</v>
       </c>
       <c r="E26">
-        <v>22.42914405306658</v>
+        <v>16.89546309105743</v>
       </c>
       <c r="F26">
         <v>60.67539285587599</v>
       </c>
       <c r="G26">
-        <v>16.89546309105743</v>
+        <v>22.42914405306658</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>24.31785543322164</v>
+      </c>
+      <c r="C27">
         <v>35.98611775969363</v>
-      </c>
-      <c r="C27">
-        <v>24.31785543322164</v>
       </c>
       <c r="D27">
         <v>2.778849351513136</v>
       </c>
       <c r="E27">
-        <v>22.44867487868608</v>
+        <v>15.16983949234789</v>
       </c>
       <c r="F27">
         <v>62.38148562896603</v>
       </c>
       <c r="G27">
-        <v>15.16983949234789</v>
+        <v>22.44867487868608</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>27.35012415750266</v>
+      </c>
+      <c r="C28">
         <v>49.52110677545229</v>
-      </c>
-      <c r="C28">
-        <v>27.35012415750266</v>
       </c>
       <c r="D28">
         <v>2.019340974212034</v>
       </c>
       <c r="E28">
-        <v>27.99839550742078</v>
+        <v>15.4632972322503</v>
       </c>
       <c r="F28">
         <v>56.53830726032892</v>
       </c>
       <c r="G28">
-        <v>15.4632972322503</v>
+        <v>27.99839550742078</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>25.9498787388844</v>
+      </c>
+      <c r="C29">
         <v>44.7696038803557</v>
-      </c>
-      <c r="C29">
-        <v>25.9498787388844</v>
       </c>
       <c r="D29">
         <v>2.233658360418924</v>
       </c>
       <c r="E29">
-        <v>26.22407424945544</v>
+        <v>15.2003030590018</v>
       </c>
       <c r="F29">
         <v>58.57562269154276</v>
       </c>
       <c r="G29">
-        <v>15.2003030590018</v>
+        <v>26.22407424945544</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>23.56959863364645</v>
+      </c>
+      <c r="C30">
         <v>46.199829205807</v>
-      </c>
-      <c r="C30">
-        <v>23.56959863364645</v>
       </c>
       <c r="D30">
         <v>2.164510166358595</v>
       </c>
       <c r="E30">
-        <v>27.21327967806841</v>
+        <v>13.88329979879276</v>
       </c>
       <c r="F30">
         <v>58.90342052313884</v>
       </c>
       <c r="G30">
-        <v>13.88329979879276</v>
+        <v>27.21327967806841</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>26.17313915857605</v>
+      </c>
+      <c r="C31">
         <v>37.45954692556634</v>
-      </c>
-      <c r="C31">
-        <v>26.17313915857605</v>
       </c>
       <c r="D31">
         <v>2.669546436285097</v>
       </c>
       <c r="E31">
-        <v>22.89245982694685</v>
+        <v>15.99505562422744</v>
       </c>
       <c r="F31">
         <v>61.11248454882571</v>
       </c>
       <c r="G31">
-        <v>15.99505562422744</v>
+        <v>22.89245982694685</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>25.80314740664866</v>
+      </c>
+      <c r="C32">
         <v>40.37619890120123</v>
-      </c>
-      <c r="C32">
-        <v>25.80314740664866</v>
       </c>
       <c r="D32">
         <v>2.476706642066421</v>
       </c>
       <c r="E32">
-        <v>24.29676117897568</v>
+        <v>15.52728902835369</v>
       </c>
       <c r="F32">
         <v>60.17594979267062</v>
       </c>
       <c r="G32">
-        <v>15.52728902835369</v>
+        <v>24.29676117897568</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>25.85929296464823</v>
+      </c>
+      <c r="C33">
         <v>47.1823591179559</v>
-      </c>
-      <c r="C33">
-        <v>25.85929296464823</v>
       </c>
       <c r="D33">
         <v>2.119436201780415</v>
       </c>
       <c r="E33">
+        <v>14.94397022533274</v>
+      </c>
+      <c r="F33">
+        <v>57.78955459363243</v>
+      </c>
+      <c r="G33">
         <v>27.26647518103483</v>
-      </c>
-      <c r="F33">
-        <v>57.78955459363242</v>
-      </c>
-      <c r="G33">
-        <v>14.94397022533274</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>34.24711180732329</v>
+      </c>
+      <c r="C34">
         <v>22.0090072449579</v>
-      </c>
-      <c r="C34">
-        <v>34.24711180732329</v>
       </c>
       <c r="D34">
         <v>4.543594306049823</v>
       </c>
       <c r="E34">
-        <v>14.08521303258146</v>
+        <v>21.91729323308271</v>
       </c>
       <c r="F34">
         <v>63.99749373433584</v>
       </c>
       <c r="G34">
-        <v>21.91729323308271</v>
+        <v>14.08521303258146</v>
       </c>
     </row>
   </sheetData>
